--- a/ResultsEnvelopeExcel.xlsx
+++ b/ResultsEnvelopeExcel.xlsx
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6">
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="7">
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.2</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="9">
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="10">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -666,1191 +666,3282 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.2011113976413736</v>
+        <v>0.2122331016682488</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7988886023586264</v>
+        <v>0.7877668983317512</v>
       </c>
       <c r="C3" t="n">
-        <v>-2038.308399891493</v>
+        <v>-1994.082458444148</v>
       </c>
       <c r="D3" t="n">
-        <v>-211.2118939065381</v>
+        <v>-245.0494549090501</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9060995509040445</v>
+        <v>0.9019802180699558</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01205145819758141</v>
+        <v>0.01465732446400156</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08748677502228458</v>
+        <v>0.1024369995630427</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9357900965975092</v>
+        <v>0.9231050166820771</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-578.6618258508428</v>
+        <v>-616.2521541694371</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02884095068356018</v>
+        <v>0.03565831568352112</v>
       </c>
       <c r="L3" t="n">
         <v>230</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.2422541421854211</v>
+        <v>0.2607926109145973</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7577458578145789</v>
+        <v>0.7392073890854027</v>
       </c>
       <c r="C4" t="n">
-        <v>-1883.542781265783</v>
+        <v>-1821.159742444437</v>
       </c>
       <c r="D4" t="n">
-        <v>-343.0695355321029</v>
+        <v>-406.8645470347213</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8869222225347506</v>
+        <v>0.8756199536008529</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02286703925593391</v>
+        <v>0.02873627770411354</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1438874860396644</v>
+        <v>0.1692441186957734</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8848499589585197</v>
+        <v>0.8589033421323575</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-716.2555602369068</v>
+        <v>-775.7022836495917</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05771879056175124</v>
+        <v>0.07383538447333936</v>
       </c>
       <c r="L4" t="n">
         <v>230</v>
       </c>
       <c r="M4" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.2787691394520064</v>
+        <v>0.3052143833969436</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7212308605479936</v>
+        <v>0.6947856166030564</v>
       </c>
       <c r="C5" t="n">
-        <v>-1764.67132679829</v>
+        <v>-1688.10278251077</v>
       </c>
       <c r="D5" t="n">
-        <v>-470.0270388549251</v>
+        <v>-564.1227072161266</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8637795291030327</v>
+        <v>0.8454993541314892</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03499249980861838</v>
+        <v>0.04526320821079523</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1931247631902527</v>
+        <v>0.2266353185729257</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8324080554172957</v>
+        <v>0.7913279317573008</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-830.9339129013525</v>
+        <v>-907.1775928476316</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09116972450222388</v>
+        <v>0.1196639750438003</v>
       </c>
       <c r="L5" t="n">
         <v>230</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.3139471519569674</v>
+        <v>0.3484106248587593</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6860528480430326</v>
+        <v>0.6515893751412407</v>
       </c>
       <c r="C6" t="n">
-        <v>-1664.32477861732</v>
+        <v>-1575.935883083739</v>
       </c>
       <c r="D6" t="n">
-        <v>-595.3941784704116</v>
+        <v>-720.4087647268051</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8393525744280476</v>
+        <v>0.8150054265592722</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04896845218657829</v>
+        <v>0.0656122508404848</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2372787935556758</v>
+        <v>0.2777787336242005</v>
       </c>
       <c r="H6" t="n">
-        <v>0.77720842304806</v>
+        <v>0.71809516810729</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-930.9818960261855</v>
+        <v>-1018.483502617158</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1298793724528091</v>
+        <v>0.1746928188410286</v>
       </c>
       <c r="L6" t="n">
         <v>230</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.134314320188525</v>
+        <v>0.3885353432531231</v>
       </c>
       <c r="B7" t="n">
-        <v>0.865685679811475</v>
+        <v>0.6114646567468769</v>
       </c>
       <c r="C7" t="n">
-        <v>-2386.983135207051</v>
+        <v>-1476.197864660976</v>
       </c>
       <c r="D7" t="n">
-        <v>-53.5808599300202</v>
+        <v>-877.5658723564778</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9058852954026878</v>
+        <v>0.7867197822373884</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002035813936235276</v>
+        <v>0.09242064819781445</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01829143714922776</v>
+        <v>0.325470441189825</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9880827592892847</v>
+        <v>0.6366269149963708</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-366.990200260212</v>
+        <v>-1110.155558968807</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00424646173824087</v>
+        <v>0.2405272179644487</v>
       </c>
       <c r="L7" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.1993217519762527</v>
+        <v>0.4176115679891513</v>
       </c>
       <c r="B8" t="n">
-        <v>0.8006782480237473</v>
+        <v>0.5823884320108487</v>
       </c>
       <c r="C8" t="n">
-        <v>-2048.552992841887</v>
+        <v>-1381.648838705262</v>
       </c>
       <c r="D8" t="n">
-        <v>-209.5136569675147</v>
+        <v>-1035.382663142482</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9053589962758769</v>
+        <v>0.7643177503963677</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01201444236425787</v>
+        <v>0.1313944753085468</v>
       </c>
       <c r="G8" t="n">
-        <v>0.08759756217735143</v>
+        <v>0.3736245950020656</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9364350682662332</v>
+        <v>0.5452636032323525</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-576.0741993472388</v>
+        <v>-1179.987423660862</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0286378648759932</v>
+        <v>0.3176821993509245</v>
       </c>
       <c r="L8" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.2399365675915892</v>
+        <v>0.4223025541211267</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7600634324084108</v>
+        <v>0.5776974458788733</v>
       </c>
       <c r="C9" t="n">
-        <v>-1892.312668809517</v>
+        <v>-1284.035272556484</v>
       </c>
       <c r="D9" t="n">
-        <v>-339.7105205673465</v>
+        <v>-1162.359070302437</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8866930364271983</v>
+        <v>0.7521444192051794</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0227774357147544</v>
+        <v>0.1875738207245956</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1441306411616994</v>
+        <v>0.4277240239854845</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8861195425106649</v>
+        <v>0.4636314540617378</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-712.2365508519006</v>
+        <v>-1213.74324129008</v>
       </c>
       <c r="K9" t="n">
-        <v>0.05724062098925289</v>
+        <v>0.3961615144776008</v>
       </c>
       <c r="L9" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.2758569579031354</v>
+        <v>0.415824024232365</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7241430420968646</v>
+        <v>0.584175975767635</v>
       </c>
       <c r="C10" t="n">
-        <v>-1772.361070498145</v>
+        <v>-1182.762611463691</v>
       </c>
       <c r="D10" t="n">
-        <v>-464.8603673192287</v>
+        <v>-1194.393402519839</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8640608144332808</v>
+        <v>0.7462112301481935</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03481718720959581</v>
+        <v>0.2379253150880633</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1935351340346473</v>
+        <v>0.4848976660670875</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8344364573300371</v>
+        <v>0.437408773172991</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-825.5435337543749</v>
+        <v>-1189.557040177865</v>
       </c>
       <c r="K10" t="n">
-        <v>0.09028261502768624</v>
+        <v>0.4474612818000529</v>
       </c>
       <c r="L10" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.3103398348039688</v>
+        <v>0.1340485127984534</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6896601651960312</v>
+        <v>0.8659514872015466</v>
       </c>
       <c r="C11" t="n">
-        <v>-1671.059198253861</v>
+        <v>-2390.476536560861</v>
       </c>
       <c r="D11" t="n">
-        <v>-588.2917640757393</v>
+        <v>-53.52183537936931</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8401363323936719</v>
+        <v>0.9056410668368794</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0486506346734742</v>
+        <v>0.002034516834923379</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2378882371391746</v>
+        <v>0.01829329058867374</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7801871304790222</v>
+        <v>0.9881108278956863</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-924.3176307296945</v>
+        <v>-366.7871375501024</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1283909280027574</v>
+        <v>0.004240469799012557</v>
       </c>
       <c r="L11" t="n">
-        <v>231</v>
+        <v>231.25</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.1332587875636936</v>
+        <v>0.2098371319923207</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8667412124363064</v>
+        <v>0.7901628680076793</v>
       </c>
       <c r="C12" t="n">
-        <v>-2400.958453824967</v>
+        <v>-2006.341081148269</v>
       </c>
       <c r="D12" t="n">
-        <v>-53.34578941675796</v>
+        <v>-242.4341686832558</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9049142049404549</v>
+        <v>0.901211930737665</v>
       </c>
       <c r="F12" t="n">
-        <v>0.002030631614419494</v>
+        <v>0.01459756063397936</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01829856742835195</v>
+        <v>0.1026130670255063</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9881946210779939</v>
+        <v>0.9240920427936299</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-366.1858067449681</v>
+        <v>-612.5673362963436</v>
       </c>
       <c r="K12" t="n">
-        <v>0.004222615315260465</v>
+        <v>0.03533176960032793</v>
       </c>
       <c r="L12" t="n">
-        <v>232</v>
+        <v>231.25</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.1975547188565006</v>
+        <v>0.2575449451864367</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8024452811434994</v>
+        <v>0.7424550548135633</v>
       </c>
       <c r="C13" t="n">
-        <v>-2058.839471849768</v>
+        <v>-1831.421070167044</v>
       </c>
       <c r="D13" t="n">
-        <v>-207.8525349677593</v>
+        <v>-401.5737107503895</v>
       </c>
       <c r="E13" t="n">
-        <v>0.904607661065843</v>
+        <v>0.8756481279834014</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01197786915185011</v>
+        <v>0.02857763028777104</v>
       </c>
       <c r="G13" t="n">
-        <v>0.08770776855201351</v>
+        <v>0.1696467928969486</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9370706191371707</v>
+        <v>0.8609352529389334</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-573.5237388905398</v>
+        <v>-769.8236705563231</v>
       </c>
       <c r="K13" t="n">
-        <v>0.028437888418372</v>
+        <v>0.07300911706244331</v>
       </c>
       <c r="L13" t="n">
-        <v>232</v>
+        <v>231.25</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.2376538737710969</v>
+        <v>0.3009471903709328</v>
       </c>
       <c r="B14" t="n">
-        <v>0.7623461262289031</v>
+        <v>0.6990528096290672</v>
       </c>
       <c r="C14" t="n">
-        <v>-1901.112729279711</v>
+        <v>-1696.815760206467</v>
       </c>
       <c r="D14" t="n">
-        <v>-336.4354934311213</v>
+        <v>-555.8948282045486</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8864386164775857</v>
+        <v>0.8463152324759554</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02268923587770725</v>
+        <v>0.04492069801520633</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1443719621707251</v>
+        <v>0.2273301163430951</v>
       </c>
       <c r="H14" t="n">
-        <v>0.887367698511397</v>
+        <v>0.7947171592454401</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-708.287099731991</v>
+        <v>-899.251777125912</v>
       </c>
       <c r="K14" t="n">
-        <v>0.05677146572301368</v>
+        <v>0.1180246793856306</v>
       </c>
       <c r="L14" t="n">
-        <v>232</v>
+        <v>231.25</v>
       </c>
       <c r="M14" t="n">
-        <v>2.2</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.2730010071244535</v>
+        <v>0.3429552699060425</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7269989928755465</v>
+        <v>0.6570447300939575</v>
       </c>
       <c r="C15" t="n">
-        <v>-1780.077802645312</v>
+        <v>-1583.240492030649</v>
       </c>
       <c r="D15" t="n">
-        <v>-459.8346021144135</v>
+        <v>-708.9565426657604</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8643014478477764</v>
+        <v>0.8165622621678801</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03464545993471708</v>
+        <v>0.06490735872776927</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1939397499704001</v>
+        <v>0.2788054926360202</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8364247534714557</v>
+        <v>0.7233482071231292</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-820.2623255085607</v>
+        <v>-1008.796830494716</v>
       </c>
       <c r="K15" t="n">
-        <v>0.08941642886071401</v>
+        <v>0.1717540042605351</v>
       </c>
       <c r="L15" t="n">
-        <v>232</v>
+        <v>231.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.3068192358120664</v>
+        <v>0.3820272034712002</v>
       </c>
       <c r="B16" t="n">
-        <v>0.6931807641879336</v>
+        <v>0.6179727965287998</v>
       </c>
       <c r="C16" t="n">
-        <v>-1677.823137738109</v>
+        <v>-1482.250288188417</v>
       </c>
       <c r="D16" t="n">
-        <v>-581.393036846318</v>
+        <v>-862.3306700084819</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8408630165915437</v>
+        <v>0.7888277905417124</v>
       </c>
       <c r="F16" t="n">
-        <v>0.04834112383904905</v>
+        <v>0.09090904162143112</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2384861562130909</v>
+        <v>0.3267654775922293</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7830970214895412</v>
+        <v>0.6446550824786557</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-917.798882523284</v>
+        <v>-1099.156828118697</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1269457940818908</v>
+        <v>0.2355646644258694</v>
       </c>
       <c r="L16" t="n">
-        <v>232</v>
+        <v>231.25</v>
       </c>
       <c r="M16" t="n">
-        <v>4.2</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.1322205890781836</v>
+        <v>0.4113461197195396</v>
       </c>
       <c r="B17" t="n">
-        <v>0.8677794109218164</v>
+        <v>0.5886538802804604</v>
       </c>
       <c r="C17" t="n">
-        <v>-2414.9487357293</v>
+        <v>-1386.9083526273</v>
       </c>
       <c r="D17" t="n">
-        <v>-53.1131334362511</v>
+        <v>-1015.373574409938</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9039601902547725</v>
+        <v>0.7664064701218768</v>
       </c>
       <c r="F17" t="n">
-        <v>0.002025460671228452</v>
+        <v>0.1277895568629341</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0183052962710013</v>
+        <v>0.3748010211675288</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9883054548714005</v>
+        <v>0.5575342901434547</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-365.3964280772645</v>
+        <v>-1168.20296377051</v>
       </c>
       <c r="K17" t="n">
-        <v>0.004199073880399863</v>
+        <v>0.3097089373820517</v>
       </c>
       <c r="L17" t="n">
-        <v>233</v>
+        <v>231.25</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.1958112114571969</v>
+        <v>0.4191240304896835</v>
       </c>
       <c r="B18" t="n">
-        <v>0.8041887885428031</v>
+        <v>0.5808759695103165</v>
       </c>
       <c r="C18" t="n">
-        <v>-2069.166887540041</v>
+        <v>-1289.480545724675</v>
       </c>
       <c r="D18" t="n">
-        <v>-206.2278384472896</v>
+        <v>-1142.676522191166</v>
       </c>
       <c r="E18" t="n">
-        <v>0.903845638857567</v>
+        <v>0.7532520309284704</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01194173907764677</v>
+        <v>0.1803700266058753</v>
       </c>
       <c r="G18" t="n">
-        <v>0.08781693355376413</v>
+        <v>0.4279064082560145</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9376968386213846</v>
+        <v>0.4775372338417635</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-571.0121905210597</v>
+        <v>-1204.205616226632</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02824099513189768</v>
+        <v>0.3861083630228632</v>
       </c>
       <c r="L18" t="n">
-        <v>233</v>
+        <v>231.25</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.235407949135424</v>
+        <v>0.4139055785534873</v>
       </c>
       <c r="B19" t="n">
-        <v>0.764592050864576</v>
+        <v>0.5860944214465127</v>
       </c>
       <c r="C19" t="n">
-        <v>-1909.942785983923</v>
+        <v>-1188.257471878591</v>
       </c>
       <c r="D19" t="n">
-        <v>-333.2429860463935</v>
+        <v>-1184.26426678587</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8861583829877918</v>
+        <v>0.746748513660578</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02260244778064335</v>
+        <v>0.2307152478372736</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1446102285773819</v>
+        <v>0.4846089919348651</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8885945072758463</v>
+        <v>0.4462537622015911</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-704.4106523519205</v>
+        <v>-1185.917076650055</v>
       </c>
       <c r="K19" t="n">
-        <v>0.05631126491938009</v>
+        <v>0.4395638036103743</v>
       </c>
       <c r="L19" t="n">
-        <v>233</v>
+        <v>231.25</v>
       </c>
       <c r="M19" t="n">
-        <v>2.2</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.2701994485580703</v>
+        <v>0.1327368041134541</v>
       </c>
       <c r="B20" t="n">
-        <v>0.7298005514419297</v>
+        <v>0.8672631958865459</v>
       </c>
       <c r="C20" t="n">
-        <v>-1787.821528798892</v>
+        <v>-2407.954817388701</v>
       </c>
       <c r="D20" t="n">
-        <v>-454.9440420636457</v>
+        <v>-53.22910265916165</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8645029370909507</v>
+        <v>0.904435452797728</v>
       </c>
       <c r="F20" t="n">
-        <v>0.03447719092765827</v>
+        <v>0.002028043718659921</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1943387268239334</v>
+        <v>0.01830206799846723</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8383741990573368</v>
+        <v>0.9882501797560397</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-815.086803974976</v>
+        <v>-365.7878685961297</v>
       </c>
       <c r="K20" t="n">
-        <v>0.08857034648051834</v>
+        <v>0.004210803238784525</v>
       </c>
       <c r="L20" t="n">
-        <v>233</v>
+        <v>232.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.3033782815211112</v>
+        <v>0.2074817459353745</v>
       </c>
       <c r="B21" t="n">
-        <v>0.6966217184788888</v>
+        <v>0.7925182540646255</v>
       </c>
       <c r="C21" t="n">
-        <v>-1684.615056857932</v>
+        <v>-2018.658078999443</v>
       </c>
       <c r="D21" t="n">
-        <v>-574.68832037161</v>
+        <v>-239.8936010313077</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8415371098102481</v>
+        <v>0.9004202415645057</v>
       </c>
       <c r="F21" t="n">
-        <v>0.04803957322679112</v>
+        <v>0.01453877056916596</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2390743657018626</v>
+        <v>0.1027873594695953</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7859405567504112</v>
+        <v>0.9250602276861524</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-911.4159863011657</v>
+        <v>-608.9547605279614</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1255413939801487</v>
+        <v>0.03501184484317554</v>
       </c>
       <c r="L21" t="n">
-        <v>233</v>
+        <v>232.5</v>
       </c>
       <c r="M21" t="n">
-        <v>4.2</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.1312016338887565</v>
+        <v>0.2543680697986332</v>
       </c>
       <c r="B22" t="n">
-        <v>0.8687983661112435</v>
+        <v>0.7456319302013668</v>
       </c>
       <c r="C22" t="n">
-        <v>-2428.942588830549</v>
+        <v>-1841.725846552024</v>
       </c>
       <c r="D22" t="n">
-        <v>-52.88298198064896</v>
+        <v>-396.4567983173516</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9030219969617378</v>
+        <v>0.8756244399295178</v>
       </c>
       <c r="F22" t="n">
-        <v>0.002020303605147072</v>
+        <v>0.02842256669265111</v>
       </c>
       <c r="G22" t="n">
-        <v>0.01831136696184499</v>
+        <v>0.1700431256617373</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9884152354745626</v>
+        <v>0.862920587518003</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-364.6258846164322</v>
+        <v>-764.0870964565131</v>
       </c>
       <c r="K22" t="n">
-        <v>0.004175842100346243</v>
+        <v>0.07220470403026739</v>
       </c>
       <c r="L22" t="n">
-        <v>234</v>
+        <v>232.5</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.1940892542644692</v>
+        <v>0.2967985987197606</v>
       </c>
       <c r="B23" t="n">
-        <v>0.8059107457355308</v>
+        <v>0.7032014012802394</v>
       </c>
       <c r="C23" t="n">
-        <v>-2079.536829474434</v>
+        <v>-1705.572386906282</v>
       </c>
       <c r="D23" t="n">
-        <v>-204.6377019079555</v>
+        <v>-547.9562241506525</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9030745927866243</v>
+        <v>0.8470508751418662</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01190602327385683</v>
+        <v>0.04458866051052095</v>
       </c>
       <c r="G23" t="n">
-        <v>0.08792563752911592</v>
+        <v>0.2280104733085113</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9383141514069397</v>
+        <v>0.7980127158523312</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-568.5354753984373</v>
+        <v>-891.5350791118694</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0280470520830511</v>
+        <v>0.1164412972259436</v>
       </c>
       <c r="L23" t="n">
-        <v>234</v>
+        <v>232.5</v>
       </c>
       <c r="M23" t="n">
-        <v>1.2</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.2331956494758466</v>
+        <v>0.3376861289386124</v>
       </c>
       <c r="B24" t="n">
-        <v>0.7668043505241534</v>
+        <v>0.6623138710613876</v>
       </c>
       <c r="C24" t="n">
-        <v>-1918.803331540049</v>
+        <v>-1590.597632072627</v>
       </c>
       <c r="D24" t="n">
-        <v>-330.1284210669658</v>
+        <v>-697.9302844491684</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8858547289604849</v>
+        <v>0.8180101179953395</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02251699038054616</v>
+        <v>0.06423253317607731</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1448465045904402</v>
+        <v>0.2798065118353872</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8898009462670116</v>
+        <v>0.7284196160342937</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>-700.6004986207189</v>
+        <v>-999.3716654980328</v>
       </c>
       <c r="K24" t="n">
-        <v>0.05585956522348118</v>
+        <v>0.1689426991919082</v>
       </c>
       <c r="L24" t="n">
-        <v>234</v>
+        <v>232.5</v>
       </c>
       <c r="M24" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.2674504459272455</v>
+        <v>0.3757494025777179</v>
       </c>
       <c r="B25" t="n">
-        <v>0.7325495540727545</v>
+        <v>0.6242505974222821</v>
       </c>
       <c r="C25" t="n">
-        <v>-1795.592237987703</v>
+        <v>-1488.35914112285</v>
       </c>
       <c r="D25" t="n">
-        <v>-450.183202236618</v>
+        <v>-847.7279444082199</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8646668065801867</v>
+        <v>0.7908164640132943</v>
       </c>
       <c r="F25" t="n">
-        <v>0.03431225740233387</v>
+        <v>0.08949502908892847</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1947322176954028</v>
+        <v>0.3280321240773819</v>
       </c>
       <c r="H25" t="n">
-        <v>0.840286011834247</v>
+        <v>0.6523075106017929</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>-810.0134488027911</v>
+        <v>-1088.444733846391</v>
       </c>
       <c r="K25" t="n">
-        <v>0.08774358262043332</v>
+        <v>0.2308721636908236</v>
       </c>
       <c r="L25" t="n">
-        <v>234</v>
+        <v>232.5</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.3000155374689403</v>
+        <v>0.4051295868023801</v>
       </c>
       <c r="B26" t="n">
-        <v>0.6999844625310597</v>
+        <v>0.5948704131976199</v>
       </c>
       <c r="C26" t="n">
-        <v>-1691.435398758481</v>
+        <v>-1392.176330110666</v>
       </c>
       <c r="D26" t="n">
-        <v>-568.1703536382909</v>
+        <v>-996.3830324423806</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8421594217553876</v>
+        <v>0.7684435039754351</v>
       </c>
       <c r="F26" t="n">
-        <v>0.04774563718683137</v>
+        <v>0.1245575201503113</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2396523371307159</v>
+        <v>0.3760042928724053</v>
       </c>
       <c r="H26" t="n">
-        <v>0.788720156617158</v>
+        <v>0.5690063449299598</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-905.1673198700983</v>
+        <v>-1156.730607585885</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1241760613254374</v>
+        <v>0.3022837063345813</v>
       </c>
       <c r="L26" t="n">
-        <v>234</v>
+        <v>232.5</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.1302009613393242</v>
+        <v>0.415490545541969</v>
       </c>
       <c r="B27" t="n">
-        <v>0.8697990386606758</v>
+        <v>0.584509454458031</v>
       </c>
       <c r="C27" t="n">
-        <v>-2442.939972039055</v>
+        <v>-1294.79785046202</v>
       </c>
       <c r="D27" t="n">
-        <v>-52.65517999938285</v>
+        <v>-1123.003495785295</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9020998520085853</v>
+        <v>0.754467717527832</v>
       </c>
       <c r="F27" t="n">
-        <v>0.002015158839844605</v>
+        <v>0.1738502556427703</v>
       </c>
       <c r="G27" t="n">
-        <v>0.01831685864841254</v>
+        <v>0.428260507623425</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9885239939179506</v>
+        <v>0.4910999169707057</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-363.8725577977149</v>
+        <v>-1194.382425930958</v>
       </c>
       <c r="K27" t="n">
-        <v>0.004152910615512228</v>
+        <v>0.3764864245728132</v>
       </c>
       <c r="L27" t="n">
-        <v>235</v>
+        <v>232.5</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.1923907453552751</v>
+        <v>0.4118164202496495</v>
       </c>
       <c r="B28" t="n">
-        <v>0.8076092546447249</v>
+        <v>0.5881835797503505</v>
       </c>
       <c r="C28" t="n">
-        <v>-2089.947315034916</v>
+        <v>-1193.676513434347</v>
       </c>
       <c r="D28" t="n">
-        <v>-203.0818669223619</v>
+        <v>-1173.089100246753</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9022940696004544</v>
+        <v>0.7473359851795921</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01187072996042502</v>
+        <v>0.2236757306061296</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0880330713498178</v>
+        <v>0.4843954388558363</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9389225513997426</v>
+        <v>0.4555315661150915</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-566.0973168698515</v>
+        <v>-1181.567335047868</v>
       </c>
       <c r="K28" t="n">
-        <v>0.02785607184297728</v>
+        <v>0.4315672145237957</v>
       </c>
       <c r="L28" t="n">
-        <v>235</v>
+        <v>232.5</v>
       </c>
       <c r="M28" t="n">
-        <v>1.2</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.2310168686620908</v>
+        <v>0.1314549271125376</v>
       </c>
       <c r="B29" t="n">
-        <v>0.7689831313379092</v>
+        <v>0.8685450728874624</v>
       </c>
       <c r="C29" t="n">
-        <v>-1927.694457564057</v>
+        <v>-2425.442560893769</v>
       </c>
       <c r="D29" t="n">
-        <v>-327.0892683596778</v>
+        <v>-52.94032152686079</v>
       </c>
       <c r="E29" t="n">
-        <v>0.885528229935582</v>
+        <v>0.9032548790849364</v>
       </c>
       <c r="F29" t="n">
-        <v>0.02243283674370417</v>
+        <v>0.002021592142240797</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1450804995184181</v>
+        <v>0.01830986999793777</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8909874409957388</v>
+        <v>0.9883878807898898</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-696.8560671339669</v>
+        <v>-364.81743047717</v>
       </c>
       <c r="K29" t="n">
-        <v>0.05541616444728947</v>
+        <v>0.004181623025074903</v>
       </c>
       <c r="L29" t="n">
-        <v>235</v>
+        <v>233.75</v>
       </c>
       <c r="M29" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.2647517128506995</v>
+        <v>0.2051668362004939</v>
       </c>
       <c r="B30" t="n">
-        <v>0.7352482871493005</v>
+        <v>0.7948331637995061</v>
       </c>
       <c r="C30" t="n">
-        <v>-1803.389810740964</v>
+        <v>-2031.033349860488</v>
       </c>
       <c r="D30" t="n">
-        <v>-445.5462629121386</v>
+        <v>-237.4248738987842</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8647948229596091</v>
+        <v>0.8996062806223947</v>
       </c>
       <c r="F30" t="n">
-        <v>0.03415052044750996</v>
+        <v>0.01448092986469198</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1951206706641729</v>
+        <v>0.1029595604055413</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8421615483894189</v>
+        <v>0.9260100702236178</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-805.037667983091</v>
+        <v>-605.4138502942366</v>
       </c>
       <c r="K30" t="n">
-        <v>0.08693531985672134</v>
+        <v>0.03469836809857967</v>
       </c>
       <c r="L30" t="n">
-        <v>235</v>
+        <v>233.75</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.2967267869616048</v>
+        <v>0.2512585773890661</v>
       </c>
       <c r="B31" t="n">
-        <v>0.7032732130383952</v>
+        <v>0.7487414226109339</v>
       </c>
       <c r="C31" t="n">
-        <v>-1698.283457947522</v>
+        <v>-1852.074199731094</v>
       </c>
       <c r="D31" t="n">
-        <v>-561.8300630277354</v>
+        <v>-391.5044882496844</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8427325329194585</v>
+        <v>0.8755518875468021</v>
       </c>
       <c r="F31" t="n">
-        <v>0.04745893005093844</v>
+        <v>0.02827091912935333</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2402209616623696</v>
+        <v>0.1704336904829835</v>
       </c>
       <c r="H31" t="n">
-        <v>0.791438591752772</v>
+        <v>0.864861257287989</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-899.0462274338915</v>
+        <v>-758.485156134062</v>
       </c>
       <c r="K31" t="n">
-        <v>0.1228477572403175</v>
+        <v>0.07142110068954365</v>
       </c>
       <c r="L31" t="n">
+        <v>233.75</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>0.2927629823415907</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0.7072370176584093</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-1714.372308288086</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-540.2915358186983</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8477098885256216</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.04426651750344513</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.2286768752645409</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.8012190251505549</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-884.0189242767547</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.1149106322301249</v>
+      </c>
+      <c r="L32" t="n">
+        <v>233.75</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>0.3325923594883016</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0.6674076405116984</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-1598.00616232421</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-687.305310837535</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8193540753304734</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.06358549348513511</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.2807828101324544</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.7333207489622968</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-990.1974558214936</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.1662496543752827</v>
+      </c>
+      <c r="L33" t="n">
+        <v>233.75</v>
+      </c>
+      <c r="M33" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>0.3696895980362638</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0.6303104019637362</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-1494.523218212109</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-833.7127455954982</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7926905950447697</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.08816762868247782</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.32927094619542</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.6596178307318734</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-1078.007503595286</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.226424960445858</v>
+      </c>
+      <c r="L34" t="n">
+        <v>233.75</v>
+      </c>
+      <c r="M34" t="n">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0.3989956863553765</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0.6010043136446235</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-1397.460404092666</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-978.3067451927933</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.770419198657942</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.1216344039250532</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.3772235124957202</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.5797802983920504</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-1145.547247013916</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.2953396456324476</v>
+      </c>
+      <c r="L35" t="n">
+        <v>233.75</v>
+      </c>
+      <c r="M35" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>0.4114821104542198</v>
+      </c>
+      <c r="B36" t="n">
+        <v>0.5885178895457802</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-1300.005062936364</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-1103.590379619073</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.7557677309602128</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.1679684167214345</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.4287644346583948</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.5041987052976376</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-1184.411508034669</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.3673311901754123</v>
+      </c>
+      <c r="L36" t="n">
+        <v>233.75</v>
+      </c>
+      <c r="M36" t="n">
+        <v>8.949999999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>0.4095292573589568</v>
+      </c>
+      <c r="B37" t="n">
+        <v>0.5904707426410432</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-1199.011453724959</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-1160.975697586517</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7479785100085024</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.2168591666084052</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.4842686899832918</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.4651657087805512</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-1176.55245255098</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.4235252438739629</v>
+      </c>
+      <c r="L37" t="n">
+        <v>233.75</v>
+      </c>
+      <c r="M37" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>0.1302009613393242</v>
+      </c>
+      <c r="B38" t="n">
+        <v>0.8697990386606758</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-2442.939972039055</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-52.65517999938285</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9020998520085853</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.002015158839844605</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.01831685864841254</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.9885239939179506</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-363.8725577977149</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.004152910615512228</v>
+      </c>
+      <c r="L38" t="n">
         <v>235</v>
       </c>
-      <c r="M31" t="n">
-        <v>4.2</v>
+      <c r="M38" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>0.2028893367753997</v>
+      </c>
+      <c r="B39" t="n">
+        <v>0.7971106632246003</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-2043.468715544727</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-235.0239492198335</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8987728473963452</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.01442398329661302</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.1031305199497858</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.9269424029835402</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-601.9381084544336</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.03439103731531422</v>
+      </c>
+      <c r="L39" t="n">
+        <v>235</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>0.2482135677202872</v>
+      </c>
+      <c r="B40" t="n">
+        <v>0.7517864322797128</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-1862.466299616389</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-386.7083367515872</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8754331809080098</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.0281225395312477</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.170818889321776</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.8667589767777988</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-753.0114858058829</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.07065736585035604</v>
+      </c>
+      <c r="L40" t="n">
+        <v>235</v>
+      </c>
+      <c r="M40" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>0.2888341621740362</v>
+      </c>
+      <c r="B41" t="n">
+        <v>0.7111658378259638</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-1723.214896398263</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-532.8858824175908</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.84829632199989</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.04395373221538282</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.2293302217031021</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.8043402429291733</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-876.6935658821449</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.1134296168019429</v>
+      </c>
+      <c r="L41" t="n">
+        <v>235</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>0.3276596055854977</v>
+      </c>
+      <c r="B42" t="n">
+        <v>0.6723403944145023</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-1605.463119274557</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-677.059391964585</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.8206018776064598</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.06296440648414618</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.2817371489781372</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.7380607023605639</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-981.2597910790763</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.163666030785262</v>
+      </c>
+      <c r="L42" t="n">
+        <v>235</v>
+      </c>
+      <c r="M42" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>0.3638350895200787</v>
+      </c>
+      <c r="B43" t="n">
+        <v>0.6361649104799213</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-1500.740763746108</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-820.2439854981836</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7944553888153667</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.08691754241694281</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.3304830862689326</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.6666153219956295</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-1067.832591730142</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.2222012136621339</v>
+      </c>
+      <c r="L43" t="n">
+        <v>235</v>
+      </c>
+      <c r="M43" t="n">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>0.3929685108305929</v>
+      </c>
+      <c r="B44" t="n">
+        <v>0.6070314891694071</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-1402.767650509845</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-961.0606914022904</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.7723260382504691</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.1189712829134451</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.3784496445833075</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.5899369710119691</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>-1134.637617346296</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.288822949210408</v>
+      </c>
+      <c r="L44" t="n">
+        <v>235</v>
+      </c>
+      <c r="M44" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>0.4071821422482182</v>
+      </c>
+      <c r="B45" t="n">
+        <v>0.5928178577517818</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-1305.122328041809</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-1084.598072692507</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.7571275143246755</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.1626619982327826</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.4293940249971311</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.5167711439311946</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-1174.391611403329</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.3586486774961645</v>
+      </c>
+      <c r="L45" t="n">
+        <v>235</v>
+      </c>
+      <c r="M45" t="n">
+        <v>8.949999999999999</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>0.407025969294239</v>
+      </c>
+      <c r="B46" t="n">
+        <v>0.592974030705761</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-1204.256660938264</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-1148.060426126167</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.7486784345092022</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.210311496908613</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.4842373174077799</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.4750671197259411</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>-1170.933753071248</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.4154942055216642</v>
+      </c>
+      <c r="L46" t="n">
+        <v>235</v>
+      </c>
+      <c r="M46" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>0.1289758550510125</v>
+      </c>
+      <c r="B47" t="n">
+        <v>0.8710241449489875</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-2460.4355642159</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-52.37363145327289</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9009692608812329</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.002008745030269338</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.01832285418070123</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.98865852076035</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>-362.9554782471266</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.004124661787809097</v>
+      </c>
+      <c r="L47" t="n">
+        <v>236.25</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>0.2006501402250008</v>
+      </c>
+      <c r="B48" t="n">
+        <v>0.7993498597749992</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-2055.963342251977</v>
+      </c>
+      <c r="D48" t="n">
+        <v>-232.6886735629306</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.8979205062119976</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.01436791673807208</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.1032995705440224</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.9278575887775835</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-598.5289915040797</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.03408973973819498</v>
+      </c>
+      <c r="L48" t="n">
+        <v>236.25</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>0.2452317022954131</v>
+      </c>
+      <c r="B49" t="n">
+        <v>0.7547682977045869</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-1872.902420152333</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-382.0613734500658</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.8752700591615008</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.0279773178601283</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.1711984121018836</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.8686150954151883</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>-747.6628611847384</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.06991275624787077</v>
+      </c>
+      <c r="L49" t="n">
+        <v>236.25</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>0.2850070281696033</v>
+      </c>
+      <c r="B50" t="n">
+        <v>0.7149929718303967</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-1732.0998106212</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-525.7260729319944</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.8488136865934617</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.04364983564181332</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.2299710262056006</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.8073800307506211</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>-869.5510667726514</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.1119955421538902</v>
+      </c>
+      <c r="L50" t="n">
+        <v>236.25</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>0.3228822454576272</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0.6771177545423728</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-1612.96896087369</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-667.1706349623405</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.8217557626918609</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.06236725680163858</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.2826690936252611</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.7426499342373121</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-972.5521221826618</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.1611847235750358</v>
+      </c>
+      <c r="L51" t="n">
+        <v>236.25</v>
+      </c>
+      <c r="M51" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>0.3581753063486475</v>
+      </c>
+      <c r="B52" t="n">
+        <v>0.6418246936513525</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-1507.010953409543</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-807.2867520984169</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.7961151089501649</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.0857370056762351</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.3316689840701184</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.6733247711513195</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>-1057.910682262592</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.2181822880858571</v>
+      </c>
+      <c r="L52" t="n">
+        <v>236.25</v>
+      </c>
+      <c r="M52" t="n">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>0.3870621222475883</v>
+      </c>
+      <c r="B53" t="n">
+        <v>0.6129378777524117</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-1408.102165389512</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-944.5706274635669</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.7741600891747562</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.1165292643579166</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.3796767954697773</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.5995448372552439</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>-1123.986128261872</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.2826877441696341</v>
+      </c>
+      <c r="L53" t="n">
+        <v>236.25</v>
+      </c>
+      <c r="M53" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>0.4026640415305994</v>
+      </c>
+      <c r="B54" t="n">
+        <v>0.5973359584694006</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-1310.167137153236</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-1066.120360553711</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.7585260238351424</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.157864865183363</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.4301278083238869</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.5287947867667427</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-1164.389221941791</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.3504261015863946</v>
+      </c>
+      <c r="L54" t="n">
+        <v>236.25</v>
+      </c>
+      <c r="M54" t="n">
+        <v>8.949999999999999</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>0.4042992218440487</v>
+      </c>
+      <c r="B55" t="n">
+        <v>0.5957007781559513</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-1209.409871882926</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-1134.497790942069</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.7494351870758184</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.204068873567404</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.4843060338839303</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.4851409420169037</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>-1164.784686973176</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.4075289862210011</v>
+      </c>
+      <c r="L55" t="n">
+        <v>236.25</v>
+      </c>
+      <c r="M55" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>0.1277786446529959</v>
+      </c>
+      <c r="B56" t="n">
+        <v>0.8722213553470041</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-2477.925642959583</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-52.09547454648996</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.899862984132316</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.002002349296346182</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.0183279046268337</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.9887914987603075</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>-362.0647656246638</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.004096863307206248</v>
+      </c>
+      <c r="L56" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>0.1984471803703052</v>
+      </c>
+      <c r="B57" t="n">
+        <v>0.8015528196296948</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-2068.51836564593</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-230.4157285807074</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8970514958646767</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.01431268554637394</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.103467221617291</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.9287563195422586</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>-595.1820141375233</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.03379423439484004</v>
+      </c>
+      <c r="L57" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>0.24231015508883</v>
+      </c>
+      <c r="B58" t="n">
+        <v>0.75768984491117</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-1883.382734949925</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-377.555842600596</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.875065137728445</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.02783511162104415</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.1715727523001729</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.8704312552972382</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>-742.4329904226929</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.06918641250504187</v>
+      </c>
+      <c r="L58" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>0.2812765934148489</v>
+      </c>
+      <c r="B59" t="n">
+        <v>0.7187234065851511</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-1741.02665370179</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-518.7993118590898</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.8492654373843138</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.04335437317759571</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.2305999244546961</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.8103419678006201</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>-862.5832549510906</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.1106058575151587</v>
+      </c>
+      <c r="L59" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="M59" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>0.3182487639677423</v>
+      </c>
+      <c r="B60" t="n">
+        <v>0.6817512360322577</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-1620.521463883408</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-657.6204289358071</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.8228221571174473</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.06179259141138543</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.2835807682174713</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.7470958479347034</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>-964.0624931311409</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.1587986513534932</v>
+      </c>
+      <c r="L60" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="M60" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>0.352698842864973</v>
+      </c>
+      <c r="B61" t="n">
+        <v>0.647301157135027</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-1513.331924155935</v>
+      </c>
+      <c r="D61" t="n">
+        <v>-794.807174820798</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.7976747799368915</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.08461915855683963</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.3328299609532928</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.6797689040812684</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>-1048.230022481146</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.2143511570567114</v>
+      </c>
+      <c r="L61" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="M61" t="n">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>0.3812865443859339</v>
+      </c>
+      <c r="B62" t="n">
+        <v>0.6187134556140661</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-1413.468007202855</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-928.7738827648215</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.7759181782490058</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.114277396971781</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.3808998260145689</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.6086608846844117</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>-1113.581230555965</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.2768958335304193</v>
+      </c>
+      <c r="L62" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="M62" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>0.3979944747922677</v>
+      </c>
+      <c r="B63" t="n">
+        <v>0.6020055252077323</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-1315.157542794664</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-1048.205229597801</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.7599433427659928</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.1535137449870376</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.4309449954828649</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.5402731577504598</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>-1154.450775283167</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.3426414074848413</v>
+      </c>
+      <c r="L63" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="M63" t="n">
+        <v>8.949999999999999</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>0.4013513081873679</v>
+      </c>
+      <c r="B64" t="n">
+        <v>0.5986486918126321</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-1214.470990279798</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-1120.446067145809</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.750246061275553</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.198155022966236</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.4844764153524315</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.4952948782114908</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>-1158.183093047852</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.3996784636680557</v>
+      </c>
+      <c r="L64" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="M64" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>0.126609322967964</v>
+      </c>
+      <c r="B65" t="n">
+        <v>0.873390677032036</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-2495.402433501311</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-51.82060422129982</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.8987803211326488</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.00199597184975752</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.01833194168865987</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.9889229434672289</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>-361.200845243261</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.004069506831090713</v>
+      </c>
+      <c r="L65" t="n">
+        <v>238.75</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>0.1962813582727621</v>
+      </c>
+      <c r="B66" t="n">
+        <v>0.8037186417272379</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-2081.132719464179</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-228.2031671047513</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.8961663607009991</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.01425827495222542</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.1036328099428264</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.9296389477673801</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>-591.8986964256009</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.03350441892731312</v>
+      </c>
+      <c r="L66" t="n">
+        <v>238.75</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>0.2394466014258273</v>
+      </c>
+      <c r="B67" t="n">
+        <v>0.7605533985741727</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-1893.907443673112</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-373.1847697219496</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.8748207421129858</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.02769579643218501</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.1719422070952402</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.8722089186918422</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>-737.3166457107518</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.0684775648900193</v>
+      </c>
+      <c r="L67" t="n">
+        <v>238.75</v>
+      </c>
+      <c r="M67" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>0.2776379323030818</v>
+      </c>
+      <c r="B68" t="n">
+        <v>0.7223620676969182</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-1749.994937005384</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-512.0933111781242</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.8496550496661206</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.04306690819515886</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.2312176910313419</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.8132295162172838</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>-855.7817589674279</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.1092581571662996</v>
+      </c>
+      <c r="L68" t="n">
+        <v>238.75</v>
+      </c>
+      <c r="M68" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>0.3137509930428695</v>
+      </c>
+      <c r="B69" t="n">
+        <v>0.6862490069571305</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-1628.119374811982</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-648.389282190691</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.8238054236006356</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.061238827135504</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.2844733862899266</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.7514068552417359</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>-955.7805716646036</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.1565014777506667</v>
+      </c>
+      <c r="L69" t="n">
+        <v>238.75</v>
+      </c>
+      <c r="M69" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>0.347394773497403</v>
+      </c>
+      <c r="B70" t="n">
+        <v>0.652605226502597</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-1519.701981588672</v>
+      </c>
+      <c r="D70" t="n">
+        <v>-782.776605741864</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.7991393686429001</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.08355832470885095</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.3339672927358557</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.6859665846533758</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-1038.780629768654</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.2106930306458656</v>
+      </c>
+      <c r="L70" t="n">
+        <v>238.75</v>
+      </c>
+      <c r="M70" t="n">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>0.3756448480556561</v>
+      </c>
+      <c r="B71" t="n">
+        <v>0.6243551519443439</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-1418.866468616954</v>
+      </c>
+      <c r="D71" t="n">
+        <v>-913.6153986272261</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.7776001166978064</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.1121906198031152</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.3821161609347177</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.6173333424926631</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>-1103.410360043475</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.2714139653031387</v>
+      </c>
+      <c r="L71" t="n">
+        <v>238.75</v>
+      </c>
+      <c r="M71" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>0.3932258648842266</v>
+      </c>
+      <c r="B72" t="n">
+        <v>0.6067741351157734</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-1320.107330885209</v>
+      </c>
+      <c r="D72" t="n">
+        <v>-1030.869678745974</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.7613642637607574</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.1495515554099659</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.431829187940048</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.5512247674347595</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>-1144.605404665508</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.3352672726371485</v>
+      </c>
+      <c r="L72" t="n">
+        <v>238.75</v>
+      </c>
+      <c r="M72" t="n">
+        <v>8.949999999999999</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>0.3981930806929466</v>
+      </c>
+      <c r="B73" t="n">
+        <v>0.6018069193070534</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-1219.44261133806</v>
+      </c>
+      <c r="D73" t="n">
+        <v>-1106.058633191896</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.7511062313249354</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.1925820897191948</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.4847468333953256</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.5054438273422752</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>-1151.207348751139</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.3919839209771151</v>
+      </c>
+      <c r="L73" t="n">
+        <v>238.75</v>
+      </c>
+      <c r="M73" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>0.1254659710788421</v>
+      </c>
+      <c r="B74" t="n">
+        <v>0.8745340289211579</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-2512.866718097327</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-51.54876587150318</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.897721637872217</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.001989610302415993</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.01833513389525671</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.9890529048308672</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>-360.3604128813031</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.004042575288330678</v>
+      </c>
+      <c r="L74" t="n">
+        <v>240</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>0.1941506175887142</v>
+      </c>
+      <c r="B75" t="n">
+        <v>0.8058493824112858</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-2093.807454000527</v>
+      </c>
+      <c r="D75" t="n">
+        <v>-226.04790723069</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.8952673291546915</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.01420464062008553</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.1037968787967021</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.9305061410576865</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-588.6745767432708</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.03322006578031362</v>
+      </c>
+      <c r="L75" t="n">
+        <v>240</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>0.2366397587667595</v>
+      </c>
+      <c r="B76" t="n">
+        <v>0.7633602412332405</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-1904.476786014668</v>
+      </c>
+      <c r="D76" t="n">
+        <v>-368.9421864773651</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.8745385416926245</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.0275592726311377</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.1723065847795285</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.8739493091018307</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>-732.310723689885</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.06778557557941579</v>
+      </c>
+      <c r="L76" t="n">
+        <v>240</v>
+      </c>
+      <c r="M76" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>0.2740871854535949</v>
+      </c>
+      <c r="B77" t="n">
+        <v>0.7259128145464051</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-1759.004511294959</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-505.5973109561296</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.8499854068465847</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.04278706500122019</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.2318246408160424</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.8160456858130299</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>-849.1401627242694</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.1079503387633071</v>
+      </c>
+      <c r="L77" t="n">
+        <v>240</v>
+      </c>
+      <c r="M77" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>0.3093823083974749</v>
+      </c>
+      <c r="B78" t="n">
+        <v>0.6906176916025251</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-1635.762211866541</v>
+      </c>
+      <c r="D78" t="n">
+        <v>-639.4612832540486</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.8247092011444619</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.06070468140758041</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.2853474349986299</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.75558972617307</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>-947.6991644067293</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.1542877863075189</v>
+      </c>
+      <c r="L78" t="n">
+        <v>240</v>
+      </c>
+      <c r="M78" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>0.3422556074668246</v>
+      </c>
+      <c r="B79" t="n">
+        <v>0.6577443925331754</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-1526.120877404715</v>
+      </c>
+      <c r="D79" t="n">
+        <v>-771.1680028788724</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.8005120086304878</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.0825493432945833</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.3350810615940161</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.691935608119806</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>-1029.55485755854</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.2071949970165038</v>
+      </c>
+      <c r="L79" t="n">
+        <v>240</v>
+      </c>
+      <c r="M79" t="n">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>0.3701392125142209</v>
+      </c>
+      <c r="B80" t="n">
+        <v>0.6298607874857791</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-1424.299301700383</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-899.0472195451014</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.779205604667664</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.1102483201554152</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.3833232245138692</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.6256035815914052</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>-1093.463611605512</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.2662138215986279</v>
+      </c>
+      <c r="L80" t="n">
+        <v>240</v>
+      </c>
+      <c r="M80" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>0.3884005046458072</v>
+      </c>
+      <c r="B81" t="n">
+        <v>0.6115994953541928</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-1325.028074287526</v>
+      </c>
+      <c r="D81" t="n">
+        <v>-1014.111542702498</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.7627764856033127</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.1459282570515527</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.4327667216393863</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.5616761897501312</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>-1134.871680472847</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.3282750351532135</v>
+      </c>
+      <c r="L81" t="n">
+        <v>240</v>
+      </c>
+      <c r="M81" t="n">
+        <v>8.949999999999999</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>0.3948434218906982</v>
+      </c>
+      <c r="B82" t="n">
+        <v>0.6051565781093018</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-1224.330207423669</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-1091.474064284489</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.7520088300750408</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.1873510774705047</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.4851124160011211</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.5155150816639782</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>-1143.931438460763</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.3844774948964669</v>
+      </c>
+      <c r="L82" t="n">
+        <v>240</v>
+      </c>
+      <c r="M82" t="n">
+        <v>10.2</v>
       </c>
     </row>
   </sheetData>
